--- a/output/full_scan/batch_seq7_2026-08-13.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-13.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1799,21 +1799,21 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6781</v>
+        <v>6739</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>531.6388249963093</v>
+        <v>565.3791324728163</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1125</v>
+        <v>1045</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.75784496279339</v>
+        <v>49.84933386412813</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.70772131656243</v>
+        <v>10.48224890951374</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6812075675506158</v>
+        <v>0.652710967577269</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,48 +1842,48 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>27.29617318376082</v>
+        <v>13.69369593672724</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6806</v>
+        <v>6781</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>531.6388249963093</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>3.51</v>
+        <v>1125</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>31.69502796334339</v>
+        <v>55.75784496279339</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>32.59319934807885</v>
+        <v>21.70772131656243</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.6812075675506158</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,48 +1895,48 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.4112821325422744</v>
+        <v>27.29617318376082</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6532</v>
+        <v>6806</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>523.7756801768195</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>87</v>
+        <v>3.51</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>65.77557388116138</v>
+        <v>31.69502796334339</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>28.7461264035022</v>
+        <v>32.59319934807885</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.129839418574075</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>3.03091793050582</v>
+        <v>0.4112821325422744</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6788</v>
+        <v>6532</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>520.9223478213482</v>
+        <v>523.7756801768195</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>363.5</v>
+        <v>87</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.67999385264918</v>
+        <v>65.77557388116138</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>27.76190100228168</v>
+        <v>28.7461264035022</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.572899931983292</v>
+        <v>1.129839418574075</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>6.60832176381339</v>
+        <v>3.03091793050582</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6597</v>
+        <v>6788</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>513.6677251862392</v>
+        <v>520.9223478213482</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>68</v>
+        <v>363.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.29117596276318</v>
+        <v>50.67999385264918</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>9.514012647957021</v>
+        <v>27.76190100228168</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8444742466786808</v>
+        <v>0.572899931983292</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0669386584714044</v>
+        <v>6.60832176381339</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6805</v>
+        <v>6597</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>505.0779235069686</v>
+        <v>513.6677251862392</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1830</v>
+        <v>68</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>63.78878098099401</v>
+        <v>52.29117596276318</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30.85367740059933</v>
+        <v>9.514012647957021</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.27496456745889</v>
+        <v>0.8444742466786808</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>58.5531809976468</v>
+        <v>0.0669386584714044</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6807</v>
+        <v>6805</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>502.5762420098295</v>
+        <v>505.0779235069686</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>38</v>
+        <v>1830</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>74.45528723082759</v>
+        <v>63.78878098099401</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.68179010771956</v>
+        <v>30.85367740059933</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.029481049328883</v>
+        <v>1.27496456745889</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3680262636577937</v>
+        <v>58.5531809976468</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6584</v>
+        <v>6807</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>498.8866495798871</v>
+        <v>502.5762420098295</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>597</v>
+        <v>38</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.26355097386514</v>
+        <v>74.45528723082759</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.97599744240152</v>
+        <v>20.68179010771956</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9192835670113714</v>
+        <v>1.029481049328883</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>16.55457207208008</v>
+        <v>0.3680262636577937</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6727</v>
+        <v>6584</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>498.5467088339622</v>
+        <v>498.8866495798871</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>393</v>
+        <v>597</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.03994799281895</v>
+        <v>57.26355097386514</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>14.98299147498243</v>
+        <v>25.97599744240152</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.262028859465542</v>
+        <v>0.9192835670113714</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>8.898036727459166</v>
+        <v>16.55457207208008</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6672</v>
+        <v>6727</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>486.1377628952446</v>
+        <v>498.5467088339622</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>264.5</v>
+        <v>393</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>59.94577855775164</v>
+        <v>51.03994799281895</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.24094693341862</v>
+        <v>14.98299147498243</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.282461164337962</v>
+        <v>1.262028859465542</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>7.176983530553903</v>
+        <v>8.898036727459166</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6691</v>
+        <v>6672</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>480.2728187882935</v>
+        <v>486.1377628952446</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>728</v>
+        <v>264.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.18303777121351</v>
+        <v>59.94577855775164</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>13.89866219305604</v>
+        <v>21.24094693341862</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6079809346050371</v>
+        <v>1.282461164337962</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>6.998181565526457</v>
+        <v>7.176983530553903</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6829</v>
+        <v>6691</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>479.8690620201465</v>
+        <v>480.2728187882935</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>222</v>
+        <v>728</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>59.50468669503221</v>
+        <v>55.18303777121351</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16.04722161746431</v>
+        <v>13.89866219305604</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.348984324244862</v>
+        <v>0.6079809346050371</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>4.736439082636447</v>
+        <v>6.998181565526457</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6510</v>
+        <v>6829</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>477.5415502922536</v>
+        <v>479.8690620201465</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2820</v>
+        <v>222</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.0776328571712</v>
+        <v>59.50468669503221</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>20.70749092967639</v>
+        <v>16.04722161746431</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9541737437525776</v>
+        <v>1.348984324244862</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>54.09912548711355</v>
+        <v>4.736439082636447</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6589</v>
+        <v>6510</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>472.2743222588467</v>
+        <v>477.5415502922536</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>50.8</v>
+        <v>2820</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>60.11889540045873</v>
+        <v>51.0776328571712</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>25.77439845438841</v>
+        <v>20.70749092967639</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9450524335911232</v>
+        <v>0.9541737437525776</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.5729789205672249</v>
+        <v>54.09912548711355</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6756</v>
+        <v>6589</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>464.7414874519964</v>
+        <v>472.2743222588467</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.52769473903533</v>
+        <v>60.11889540045873</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>15.14327173823001</v>
+        <v>25.77439845438841</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9164767988572564</v>
+        <v>0.9450524335911232</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.7993497560811187</v>
+        <v>0.5729789205672249</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6504</v>
+        <v>6756</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>460.414023692824</v>
+        <v>464.7414874519964</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>38.25</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.12902701378209</v>
+        <v>54.52769473903533</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>28.02644348763386</v>
+        <v>15.14327173823001</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5291468245191681</v>
+        <v>0.9164767988572564</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.1533786258226093</v>
+        <v>0.7993497560811187</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6546</v>
+        <v>6504</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>452.4198637867253</v>
+        <v>460.414023692824</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>66</v>
+        <v>38.25</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>57.78334092921236</v>
+        <v>50.12902701378209</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>30.62753936197033</v>
+        <v>28.02644348763386</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3.787708250970692</v>
+        <v>0.5291468245191681</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.588575306211666</v>
+        <v>-0.1533786258226093</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6770</v>
+        <v>6546</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>449.7002764429392</v>
+        <v>452.4198637867253</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>61.26373929911581</v>
+        <v>57.78334092921236</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15.4769052578571</v>
+        <v>30.62753936197033</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2.270027644293921</v>
+        <v>3.787708250970692</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>2.13459150476115</v>
+        <v>1.588575306211666</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6799</v>
+        <v>6770</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>440.7172826187211</v>
+        <v>449.7002764429392</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.59145046623271</v>
+        <v>61.26373929911581</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.05581490893999</v>
+        <v>15.4769052578571</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.2829155735352259</v>
+        <v>2.270027644293921</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.281423433531484</v>
+        <v>2.13459150476115</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6505</v>
+        <v>6799</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>438.1793795009783</v>
+        <v>440.7172826187211</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>69.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.07855199511643</v>
+        <v>49.59145046623271</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>27.7374494167803</v>
+        <v>20.05581490893999</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2177866457636232</v>
+        <v>0.2829155735352259</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.207769330267384</v>
+        <v>1.281423433531484</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6548</v>
+        <v>6505</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>435.0521483943845</v>
+        <v>438.1793795009783</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>74.5</v>
+        <v>69.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.22499969666168</v>
+        <v>50.07855199511643</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17.11727155639245</v>
+        <v>27.7374494167803</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4461786441013731</v>
+        <v>0.2177866457636232</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.209274448924492</v>
+        <v>-1.207769330267384</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6530</v>
+        <v>6548</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>423.2836128342956</v>
+        <v>435.0521483943845</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>85.8</v>
+        <v>74.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>57.28944619422469</v>
+        <v>51.22499969666168</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.59302452956486</v>
+        <v>17.11727155639245</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.834847389957138</v>
+        <v>0.4461786441013731</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>2.666565996531028</v>
+        <v>1.209274448924492</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6526</v>
+        <v>6530</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>422.329479933347</v>
+        <v>423.2836128342956</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>624</v>
+        <v>85.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>53.83886093575956</v>
+        <v>57.28944619422469</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15.35292070175989</v>
+        <v>22.59302452956486</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5542136234665451</v>
+        <v>2.834847389957138</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>10.59755789505117</v>
+        <v>2.666565996531028</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6517</v>
+        <v>6526</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>421.5383526946082</v>
+        <v>422.329479933347</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>63.7</v>
+        <v>624</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>47.08100707139351</v>
+        <v>53.83886093575956</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.20020864520854</v>
+        <v>15.35292070175989</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4652715652574628</v>
+        <v>0.5542136234665451</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0540359291175871</v>
+        <v>10.59755789505117</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6763</v>
+        <v>6517</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>410.982191942297</v>
+        <v>421.5383526946082</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>42.85</v>
+        <v>63.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.82835155718937</v>
+        <v>47.08100707139351</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>25.02419889514221</v>
+        <v>16.20020864520854</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4968266866905994</v>
+        <v>0.4652715652574628</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.3283479115650549</v>
+        <v>-0.0540359291175871</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6533</v>
+        <v>6763</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>408.2277726248292</v>
+        <v>410.982191942297</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>249.5</v>
+        <v>42.85</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>61.70787743407196</v>
+        <v>47.82835155718937</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.565849192008</v>
+        <v>25.02419889514221</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5453824773727142</v>
+        <v>0.4968266866905994</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>3.322050141392706</v>
+        <v>0.3283479115650549</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6585</v>
+        <v>6533</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>407.0374625518612</v>
+        <v>408.2277726248292</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>120</v>
+        <v>249.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.7236559847781</v>
+        <v>61.70787743407196</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16.35072553769538</v>
+        <v>16.565849192008</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4345435613602557</v>
+        <v>0.5453824773727142</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.360891012927574</v>
+        <v>3.322050141392706</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6485</v>
+        <v>6585</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>392.7865048014315</v>
+        <v>407.0374625518612</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>120</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.6143995642172</v>
+        <v>50.7236559847781</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>26.66269260164455</v>
+        <v>16.35072553769538</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7241540757278374</v>
+        <v>0.4345435613602557</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.873941921903262</v>
+        <v>0.360891012927574</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6592</v>
+        <v>6485</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>391.4448402195299</v>
+        <v>392.7865048014315</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>61.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>55.09629142754447</v>
+        <v>49.6143995642172</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>11.2072472292575</v>
+        <v>26.66269260164455</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8069530500899972</v>
+        <v>0.7241540757278374</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.2185106887053656</v>
+        <v>1.873941921903262</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6689</v>
+        <v>6592</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>389.4192521415363</v>
+        <v>391.4448402195299</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>63.5</v>
+        <v>61.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.5499367334045</v>
+        <v>55.09629142754447</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.29307059250384</v>
+        <v>11.2072472292575</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8620903063003591</v>
+        <v>0.8069530500899972</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.7531867361078162</v>
+        <v>0.2185106887053656</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6643</v>
+        <v>6689</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>387.8861367136258</v>
+        <v>389.4192521415363</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>447.5</v>
+        <v>63.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.50847002590299</v>
+        <v>54.5499367334045</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.85099116037014</v>
+        <v>21.29307059250384</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8842863864963173</v>
+        <v>0.8620903063003591</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>8.588912875281599</v>
+        <v>0.7531867361078162</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6654</v>
+        <v>6643</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>381.630650104766</v>
+        <v>387.8861367136258</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>181</v>
+        <v>447.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>55.53392096478769</v>
+        <v>52.50847002590299</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.34462427613047</v>
+        <v>18.85099116037014</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.155298113260916</v>
+        <v>0.8842863864963173</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.803078900640267</v>
+        <v>8.588912875281599</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6640</v>
+        <v>6654</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>377.6909510913088</v>
+        <v>381.630650104766</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>995</v>
+        <v>181</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>53.31723503339638</v>
+        <v>55.53392096478769</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>19.38048023762264</v>
+        <v>18.34462427613047</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.167585064536784</v>
+        <v>1.155298113260916</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>23.69462983223441</v>
+        <v>1.803078900640267</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, cci_momentum</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6666</v>
+        <v>6640</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>374.9107921081634</v>
+        <v>377.6909510913088</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>42.65</v>
+        <v>995</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.36229981576009</v>
+        <v>53.31723503339638</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>30.87013301758816</v>
+        <v>19.38048023762264</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7577976623548421</v>
+        <v>1.167585064536784</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.2598915014942597</v>
+        <v>23.69462983223441</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6494</v>
+        <v>6666</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>372.5334447675029</v>
+        <v>374.9107921081634</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>53.9</v>
+        <v>42.65</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.41813117354531</v>
+        <v>43.36229981576009</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22.41955722586568</v>
+        <v>30.87013301758816</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6059778279878705</v>
+        <v>0.7577976623548421</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.121790791764916</v>
+        <v>-0.2598915014942597</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6693</v>
+        <v>6494</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>371.8649085121635</v>
+        <v>372.5334447675029</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>185</v>
+        <v>53.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.00577670198603</v>
+        <v>50.41813117354531</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>22.46103052255724</v>
+        <v>22.41955722586568</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.497065463783021</v>
+        <v>0.6059778279878705</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>3.192648360741991</v>
+        <v>1.121790791764916</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6821</v>
+        <v>6693</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>371.1482984064796</v>
+        <v>371.8649085121635</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>43.12829268495742</v>
+        <v>51.00577670198603</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.16025297565197</v>
+        <v>22.46103052255724</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.034965071400752</v>
+        <v>1.497065463783021</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.9324472465659132</v>
+        <v>3.192648360741991</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6605</v>
+        <v>6821</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>369.3138546373718</v>
+        <v>371.1482984064796</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>136.5</v>
+        <v>43</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.75947789678682</v>
+        <v>43.12829268495742</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.64831751216909</v>
+        <v>28.16025297565197</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7222075861351392</v>
+        <v>1.034965071400752</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.6233162667311183</v>
+        <v>0.9324472465659132</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6706</v>
+        <v>6605</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>367.8051387928279</v>
+        <v>369.3138546373718</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>122.5</v>
+        <v>136.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.3755880663484</v>
+        <v>52.75947789678682</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>23.36460474397057</v>
+        <v>12.64831751216909</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8431223528482433</v>
+        <v>0.7222075861351392</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>4.286729379966468</v>
+        <v>0.6233162667311183</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6577</v>
+        <v>6706</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>362.4222158503363</v>
+        <v>367.8051387928279</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>79.5</v>
+        <v>122.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.40645441361617</v>
+        <v>52.3755880663484</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.08599182028461</v>
+        <v>23.36460474397057</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.1883145548949289</v>
+        <v>0.8431223528482433</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.2670852375813327</v>
+        <v>4.286729379966468</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6830</v>
+        <v>6577</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>360.5789029866918</v>
+        <v>362.4222158503363</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>420.5</v>
+        <v>79.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.47311947012582</v>
+        <v>49.40645441361617</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.25641415578155</v>
+        <v>23.08599182028461</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.980739383128742</v>
+        <v>0.1883145548949289</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>13.54318826445689</v>
+        <v>-0.2670852375813327</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6613</v>
+        <v>6830</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>356.3800066847713</v>
+        <v>360.5789029866918</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>270.5</v>
+        <v>420.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>41.36222077665525</v>
+        <v>51.47311947012582</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.03463185405442</v>
+        <v>19.25641415578155</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.240759642973474</v>
+        <v>0.980739383128742</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.068325791601783</v>
+        <v>13.54318826445689</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6670</v>
+        <v>6613</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>356.3071788874115</v>
+        <v>356.3800066847713</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>267</v>
+        <v>270.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.39460174768182</v>
+        <v>41.36222077665525</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12.28256217748137</v>
+        <v>15.03463185405442</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.665485702499458</v>
+        <v>1.240759642973474</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.6848574695101624</v>
+        <v>-2.068325791601783</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6742</v>
+        <v>6670</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>354.2539102248634</v>
+        <v>356.3071788874115</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>43.9</v>
+        <v>267</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.56385898418064</v>
+        <v>53.39460174768182</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.56808254848057</v>
+        <v>12.28256217748137</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3713481851001997</v>
+        <v>0.665485702499458</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.6645166947290413</v>
+        <v>0.6848574695101624</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6715</v>
+        <v>6742</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>353.7694556453644</v>
+        <v>354.2539102248634</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>390.5</v>
+        <v>43.9</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.94378816463318</v>
+        <v>41.56385898418064</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>10.62489755929594</v>
+        <v>20.56808254848057</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.798540505847586</v>
+        <v>0.3713481851001997</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>7.231007660877463</v>
+        <v>0.6645166947290413</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6525</v>
+        <v>6715</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>345.720769808407</v>
+        <v>353.7694556453644</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>150.5</v>
+        <v>390.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.35845739143687</v>
+        <v>51.94378816463318</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.72929889450225</v>
+        <v>10.62489755929594</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.412132993746048</v>
+        <v>1.798540505847586</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.510925420472423</v>
+        <v>7.231007660877463</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6515</v>
+        <v>6525</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>338.9404285570494</v>
+        <v>345.720769808407</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>6745</v>
+        <v>150.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>47.54076037724206</v>
+        <v>53.35845739143687</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.03806604888676</v>
+        <v>18.72929889450225</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.903260584118084</v>
+        <v>1.412132993746048</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>182.38994232722</v>
+        <v>1.510925420472423</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6803</v>
+        <v>6515</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>335.8320012049597</v>
+        <v>338.9404285570494</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>268.5</v>
+        <v>6745</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>36.99344487290612</v>
+        <v>47.54076037724206</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>34.25642624168293</v>
+        <v>16.03806604888676</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.07454900852527</v>
+        <v>1.903260584118084</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.3152581071674474</v>
+        <v>182.38994232722</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6588</v>
+        <v>6803</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>331.6775537357637</v>
+        <v>335.8320012049597</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>93.7</v>
+        <v>268.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.27298596518748</v>
+        <v>36.99344487290612</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.55609748006309</v>
+        <v>34.25642624168293</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.790199103844344</v>
+        <v>1.07454900852527</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.570955417887546</v>
+        <v>0.3152581071674474</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6789</v>
+        <v>6588</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>329.1596853463571</v>
+        <v>331.6775537357637</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>451</v>
+        <v>93.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.800052817433</v>
+        <v>54.27298596518748</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>22.05599120488768</v>
+        <v>18.55609748006309</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6036103072406287</v>
+        <v>0.790199103844344</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>3.762804667252226</v>
+        <v>1.570955417887546</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6743</v>
+        <v>6789</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>327.9346532720603</v>
+        <v>329.1596853463571</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>26.85</v>
+        <v>451</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.61859206454999</v>
+        <v>47.800052817433</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25.85864406468626</v>
+        <v>22.05599120488768</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7481744158748594</v>
+        <v>0.6036103072406287</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1812168885513689</v>
+        <v>3.762804667252226</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6732</v>
+        <v>6743</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>327.3976420408724</v>
+        <v>327.9346532720603</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>156.5</v>
+        <v>26.85</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>41.55788392969235</v>
+        <v>41.61859206454999</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20.05451319538315</v>
+        <v>25.85864406468626</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2576236511493071</v>
+        <v>0.7481744158748594</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.6136050650143972</v>
+        <v>-0.1812168885513689</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6796</v>
+        <v>6732</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>323.2839463008293</v>
+        <v>327.3976420408724</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>60</v>
+        <v>156.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>56.81792110591461</v>
+        <v>41.55788392969235</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.15485194167612</v>
+        <v>20.05451319538315</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.28267946143788</v>
+        <v>0.2576236511493071</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5346517032440588</v>
+        <v>-0.6136050650143972</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6792</v>
+        <v>6796</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>322.1203017997678</v>
+        <v>323.2839463008293</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>59.5</v>
+        <v>60</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>57.64371421527161</v>
+        <v>56.81792110591461</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.31974423845987</v>
+        <v>20.15485194167612</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.004100734425318</v>
+        <v>1.28267946143788</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>1.065862496426043</v>
+        <v>0.5346517032440588</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6561</v>
+        <v>6792</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>317.3806701115241</v>
+        <v>322.1203017997678</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>325.5</v>
+        <v>59.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.20593069887378</v>
+        <v>57.64371421527161</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.09539410161987</v>
+        <v>17.31974423845987</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.228193370664352</v>
+        <v>1.004100734425318</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.9717051515368084</v>
+        <v>1.065862496426043</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6684</v>
+        <v>6561</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>313.5768019149614</v>
+        <v>317.3806701115241</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>49.95</v>
+        <v>325.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.78658881378053</v>
+        <v>47.20593069887378</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>15.44973996110632</v>
+        <v>14.09539410161987</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5787567360818285</v>
+        <v>1.228193370664352</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4817516764816392</v>
+        <v>0.9717051515368084</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6680</v>
+        <v>6684</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>308.2601388604533</v>
+        <v>313.5768019149614</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0</v>
+        <v>49.95</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>37.67311894060075</v>
+        <v>50.78658881378053</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>9.28854717580642</v>
+        <v>15.44973996110632</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0</v>
+        <v>0.5787567360818285</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-3.258268985064576</v>
+        <v>0.4817516764816392</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6720</v>
+        <v>6680</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>304.5389642715614</v>
+        <v>308.2601388604533</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.27969449093182</v>
+        <v>37.67311894060075</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>24.47917017191804</v>
+        <v>9.28854717580642</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3411058583376072</v>
+        <v>0</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.768254440699419</v>
+        <v>-3.258268985064576</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6645</v>
+        <v>6720</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>300.6563843027555</v>
+        <v>304.5389642715614</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>13.6</v>
+        <v>138</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.58318436975105</v>
+        <v>49.27969449093182</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>24.26050168208126</v>
+        <v>24.47917017191804</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.456207937809342</v>
+        <v>0.3411058583376072</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0445020156505799</v>
+        <v>0.768254440699419</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6692</v>
+        <v>6645</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>293.1581211112981</v>
+        <v>300.6563843027555</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>24</v>
+        <v>13.6</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.86560615645588</v>
+        <v>47.58318436975105</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>10.47148798760832</v>
+        <v>24.26050168208126</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.550271238833239</v>
+        <v>1.456207937809342</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.5101119339614918</v>
+        <v>0.0445020156505799</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6835</v>
+        <v>6692</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>287.6960875709941</v>
+        <v>293.1581211112981</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>31.4</v>
+        <v>24</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>43.42485315715592</v>
+        <v>51.86560615645588</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>34.91625536594213</v>
+        <v>10.47148798760832</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4826880571619154</v>
+        <v>1.550271238833239</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2472208263431148</v>
+        <v>0.5101119339614918</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6671</v>
+        <v>6835</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>278.6421485071237</v>
+        <v>287.6960875709941</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>22.9</v>
+        <v>31.4</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>40.05927845151759</v>
+        <v>43.42485315715592</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>29.94029891175663</v>
+        <v>34.91625536594213</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.1398415595130717</v>
+        <v>0.4826880571619154</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.09533934049876409</v>
+        <v>0.2472208263431148</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6550</v>
+        <v>6671</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>277.3373111836889</v>
+        <v>278.6421485071237</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>11.1</v>
+        <v>22.9</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>37.54670978765229</v>
+        <v>40.05927845151759</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>26.27137197311162</v>
+        <v>29.94029891175663</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8799366771261588</v>
+        <v>0.1398415595130717</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0428929396573474</v>
+        <v>0.09533934049876409</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6776</v>
+        <v>6550</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>275.8607646486146</v>
+        <v>277.3373111836889</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>54.5</v>
+        <v>11.1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>50.48617537881431</v>
+        <v>37.54670978765229</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>20.31242972670404</v>
+        <v>26.27137197311162</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7980456577945443</v>
+        <v>0.8799366771261588</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1768356138407552</v>
+        <v>0.0428929396573474</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6679</v>
+        <v>6776</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>275.6186813994543</v>
+        <v>275.8607646486146</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>213</v>
+        <v>54.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.86095576859813</v>
+        <v>50.48617537881431</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>28.14997774739763</v>
+        <v>20.31242972670404</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6334988978795419</v>
+        <v>0.7980456577945443</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>2.28767422204621</v>
+        <v>0.1768356138407552</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6719</v>
+        <v>6679</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>274.1610105470582</v>
+        <v>275.6186813994543</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.31445665645482</v>
+        <v>42.86095576859813</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>20.18354820387589</v>
+        <v>28.14997774739763</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9910474371511986</v>
+        <v>0.6334988978795419</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.6575808680900934</v>
+        <v>2.28767422204621</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6568</v>
+        <v>6719</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>264.556418583624</v>
+        <v>274.1610105470582</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.96009384978073</v>
+        <v>42.31445665645482</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>47.83481990387092</v>
+        <v>20.18354820387589</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5252600045134808</v>
+        <v>0.9910474371511986</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>2.30757334649452</v>
+        <v>0.6575808680900934</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6735</v>
+        <v>6568</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>262.5953710963074</v>
+        <v>264.556418583624</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>65.7</v>
+        <v>137</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>42.0273057076194</v>
+        <v>41.96009384978073</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>24.50326166316791</v>
+        <v>47.83481990387092</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.9086011593785454</v>
+        <v>0.5252600045134808</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>1.231120955673886</v>
+        <v>2.30757334649452</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6558</v>
+        <v>6735</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>258.7921336155913</v>
+        <v>262.5953710963074</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>26.1</v>
+        <v>65.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>45.82562550091473</v>
+        <v>42.0273057076194</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>28.3745072056989</v>
+        <v>24.50326166316791</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7591742068289725</v>
+        <v>0.9086011593785454</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.342598365526032</v>
+        <v>1.231120955673886</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6560</v>
+        <v>6558</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>258.641482766928</v>
+        <v>258.7921336155913</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>31.7</v>
+        <v>26.1</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.00507364436372</v>
+        <v>45.82562550091473</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>21.10414007055723</v>
+        <v>28.3745072056989</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.25654171382915</v>
+        <v>0.7591742068289725</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.2188863588938576</v>
+        <v>0.342598365526032</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6579</v>
+        <v>6560</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>253.7841616501585</v>
+        <v>258.641482766928</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>157</v>
+        <v>31.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.66732010264089</v>
+        <v>37.00507364436372</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.78074491097273</v>
+        <v>21.10414007055723</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5493213760722755</v>
+        <v>1.25654171382915</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.997756438750407</v>
+        <v>0.2188863588938576</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6624</v>
+        <v>6579</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>250.0556579754775</v>
+        <v>253.7841616501585</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>40.4</v>
+        <v>157</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>52.93484348169444</v>
+        <v>45.66732010264089</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9.818123633789527</v>
+        <v>11.78074491097273</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2133133381133722</v>
+        <v>0.5493213760722755</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>2.84262591258244</v>
+        <v>-0.997756438750407</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6498</v>
+        <v>6624</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>243.5790772179371</v>
+        <v>250.0556579754775</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>74.5</v>
+        <v>40.4</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.677682279872</v>
+        <v>52.93484348169444</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>35.77484100663625</v>
+        <v>9.818123633789527</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5399132501782867</v>
+        <v>0.2133133381133722</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.8665098934274615</v>
+        <v>2.84262591258244</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6641</v>
+        <v>6498</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>239</v>
+        <v>243.5790772179371</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>17.8</v>
+        <v>74.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.52395917122324</v>
+        <v>40.677682279872</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>10.33142692021286</v>
+        <v>35.77484100663625</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>10.49461333205318</v>
+        <v>0.5399132501782867</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0552519006814052</v>
+        <v>0.8665098934274615</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6768</v>
+        <v>6641</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>237.5901850398914</v>
+        <v>239</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>66</v>
+        <v>17.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>34.46676013281585</v>
+        <v>47.52395917122324</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>34.54759900217145</v>
+        <v>10.33142692021286</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8465544301080802</v>
+        <v>10.49461333205318</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.2629116391285713</v>
+        <v>0.0552519006814052</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6668</v>
+        <v>6768</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>232.1240367792088</v>
+        <v>237.5901850398914</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>36.4</v>
+        <v>66</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.19588332961931</v>
+        <v>34.46676013281585</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.93513645136043</v>
+        <v>34.54759900217145</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5560501264624468</v>
+        <v>0.8465544301080802</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.3790894509985478</v>
+        <v>0.2629116391285713</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6582</v>
+        <v>6668</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>231.9798962314564</v>
+        <v>232.1240367792088</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>31.55</v>
+        <v>36.4</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.65088631754661</v>
+        <v>51.19588332961931</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.23416807319237</v>
+        <v>15.93513645136043</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.071038271592372</v>
+        <v>0.5560501264624468</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0307054380353444</v>
+        <v>0.3790894509985478</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6708</v>
+        <v>6582</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>229.9027996190156</v>
+        <v>231.9798962314564</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>37.9</v>
+        <v>31.55</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>51.60781107958747</v>
+        <v>43.65088631754661</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>11.65425540809064</v>
+        <v>16.23416807319237</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3635100368041325</v>
+        <v>1.071038271592372</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>2.033381222339594</v>
+        <v>-0.0307054380353444</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6757</v>
+        <v>6708</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>228.7599367090667</v>
+        <v>229.9027996190156</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>54.4</v>
+        <v>37.9</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.59608411175196</v>
+        <v>51.60781107958747</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.05850154345742</v>
+        <v>11.65425540809064</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.9028534596178855</v>
+        <v>0.3635100368041325</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.06868541123442611</v>
+        <v>2.033381222339594</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6657</v>
+        <v>6757</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>228.5055545861255</v>
+        <v>228.7599367090667</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>31.55</v>
+        <v>54.4</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>44.05850327982203</v>
+        <v>41.59608411175196</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>28.00708822781383</v>
+        <v>12.05850154345742</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7899415149609371</v>
+        <v>0.9028534596178855</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1226907680418116</v>
+        <v>-0.06868541123442611</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6486</v>
+        <v>6657</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>228.4347727058869</v>
+        <v>228.5055545861255</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>74.2</v>
+        <v>31.55</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.40708271613121</v>
+        <v>44.05850327982203</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>21.42014343468962</v>
+        <v>28.00708822781383</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.007015447081263</v>
+        <v>0.7899415149609371</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.115985974520129</v>
+        <v>0.1226907680418116</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6698</v>
+        <v>6486</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>227.5154348850891</v>
+        <v>228.4347727058869</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>32.1</v>
+        <v>74.2</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>38.60203004566394</v>
+        <v>35.40708271613121</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>23.54995595043031</v>
+        <v>21.42014343468962</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.368454727700152</v>
+        <v>1.007015447081263</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1665229749795693</v>
+        <v>0.115985974520129</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6581</v>
+        <v>6698</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>217.2548790815714</v>
+        <v>227.5154348850891</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>107.5</v>
+        <v>32.1</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.05119249836668</v>
+        <v>38.60203004566394</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.49510684884112</v>
+        <v>23.54995595043031</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5575534971686024</v>
+        <v>1.368454727700152</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.09926302783715139</v>
+        <v>0.1665229749795693</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6655</v>
+        <v>6581</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>216.0494785848274</v>
+        <v>217.2548790815714</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>117</v>
+        <v>107.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.68906589147208</v>
+        <v>46.05119249836668</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>5.917202648978922</v>
+        <v>13.49510684884112</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.785630916872001</v>
+        <v>0.5575534971686024</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0714493480504125</v>
+        <v>-0.09926302783715139</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6725</v>
+        <v>6655</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>215.8478395114926</v>
+        <v>216.0494785848274</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>245</v>
+        <v>117</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>37.00789714933144</v>
+        <v>47.68906589147208</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>24.05086399274153</v>
+        <v>5.917202648978922</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.735260180290885</v>
+        <v>0.785630916872001</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2464276527997135</v>
+        <v>-0.0714493480504125</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6674</v>
+        <v>6725</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>213.847365624161</v>
+        <v>215.8478395114926</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>15.05</v>
+        <v>245</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>33.33068307888834</v>
+        <v>37.00789714933144</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>26.97264638889474</v>
+        <v>24.05086399274153</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3363385808380436</v>
+        <v>1.735260180290885</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0075529091660008</v>
+        <v>-0.2464276527997135</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6722</v>
+        <v>6674</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>210.6709361278374</v>
+        <v>213.847365624161</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>32.8</v>
+        <v>15.05</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>37.98317283085282</v>
+        <v>33.33068307888834</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>43.60879446018073</v>
+        <v>26.97264638889474</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7440402961270689</v>
+        <v>0.3363385808380436</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.070753362987772</v>
+        <v>0.0075529091660008</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6667</v>
+        <v>6722</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>192.1287251992492</v>
+        <v>210.6709361278374</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>225.5</v>
+        <v>32.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>40.32735937613213</v>
+        <v>37.98317283085282</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>26.67160283388829</v>
+        <v>43.60879446018073</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.9527891424531472</v>
+        <v>0.7440402961270689</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.92158664474319</v>
+        <v>0.070753362987772</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6790</v>
+        <v>6667</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>191.5285280528013</v>
+        <v>192.1287251992492</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>38</v>
+        <v>225.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>35.6365752962183</v>
+        <v>40.32735937613213</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.97045697964927</v>
+        <v>26.67160283388829</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.530904021970774</v>
+        <v>0.9527891424531472</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0225146353383976</v>
+        <v>0.92158664474319</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6695</v>
+        <v>6790</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>184.0807219251039</v>
+        <v>191.5285280528013</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>51.5</v>
+        <v>38</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.01175200379634</v>
+        <v>35.6365752962183</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>15.17594444733711</v>
+        <v>17.97045697964927</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.574484280262953</v>
+        <v>1.530904021970774</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.2493115722367902</v>
+        <v>-0.0225146353383976</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6838</v>
+        <v>6695</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>180.648387761942</v>
+        <v>184.0807219251039</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>23.05</v>
+        <v>51.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>40.47599587594518</v>
+        <v>49.01175200379634</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>10.95889845988403</v>
+        <v>15.17594444733711</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6325239377437545</v>
+        <v>0.574484280262953</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0354108380662371</v>
+        <v>0.2493115722367902</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6556</v>
+        <v>6838</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>179.6349075975184</v>
+        <v>180.648387761942</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>59.8</v>
+        <v>23.05</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>34.13331689294701</v>
+        <v>40.47599587594518</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>23.54953655873665</v>
+        <v>10.95889845988403</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.083606808923471</v>
+        <v>0.6325239377437545</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.3345869550126708</v>
+        <v>-0.0354108380662371</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6794</v>
+        <v>6556</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>176.5467573333656</v>
+        <v>179.6349075975184</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>71</v>
+        <v>59.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>28.49208339771172</v>
+        <v>34.13331689294701</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.30692074389971</v>
+        <v>23.54953655873665</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>2.906848050783551</v>
+        <v>1.083606808923471</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.2839529906419646</v>
+        <v>-0.3345869550126708</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6754</v>
+        <v>6794</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>175.1695017941672</v>
+        <v>176.5467573333656</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>41.95</v>
+        <v>71</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.37994312389414</v>
+        <v>28.49208339771172</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>9.082114428417778</v>
+        <v>13.30692074389971</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.478933077783102</v>
+        <v>2.906848050783551</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0703866765549022</v>
+        <v>-0.2839529906419646</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6573</v>
+        <v>6754</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>170.6956536540289</v>
+        <v>175.1695017941672</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>16.85</v>
+        <v>41.95</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.32686163931295</v>
+        <v>43.37994312389414</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.12851377026</v>
+        <v>9.082114428417778</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.518504300847429</v>
+        <v>1.478933077783102</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.113088362250827</v>
+        <v>0.0703866765549022</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6625</v>
+        <v>6573</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>163.0199591235359</v>
+        <v>170.6956536540289</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>77.5</v>
+        <v>16.85</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>54.09309124662025</v>
+        <v>42.32686163931295</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.30653069311032</v>
+        <v>15.12851377026</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6107194492939755</v>
+        <v>0.518504300847429</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.2572762250669</v>
+        <v>-0.113088362250827</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6541</v>
+        <v>6625</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>144.9427655085289</v>
+        <v>163.0199591235359</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>38.1</v>
+        <v>77.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.62304335026393</v>
+        <v>54.09309124662025</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.476562791682261</v>
+        <v>14.30653069311032</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.137731630423132</v>
+        <v>0.6107194492939755</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.1274512549429474</v>
+        <v>0.2572762250669</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6823</v>
+        <v>6541</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>139.3090504660309</v>
+        <v>144.9427655085289</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>62.8</v>
+        <v>38.1</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.40787334991528</v>
+        <v>45.62304335026393</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.3151016854226</v>
+        <v>9.476562791682261</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5741473874757492</v>
+        <v>1.137731630423132</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.1517070975779106</v>
+        <v>0.1274512549429474</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6512</v>
+        <v>6823</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>138.9065221275126</v>
+        <v>139.3090504660309</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>20</v>
+        <v>62.8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>52.75610671808796</v>
+        <v>43.40787334991528</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>8.980299258802113</v>
+        <v>12.3151016854226</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>3.024616851436744</v>
+        <v>0.5741473874757492</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.5487227995965747</v>
+        <v>0.1517070975779106</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6614</v>
+        <v>6512</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>131.8118564390042</v>
+        <v>138.9065221275126</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>33.92560719041563</v>
+        <v>52.75610671808796</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>15.71215195376678</v>
+        <v>8.980299258802113</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.2248369848150129</v>
+        <v>3.024616851436744</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,62 +7089,115 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0131129154176956</v>
+        <v>0.5487227995965747</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
+        <v>6614</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>131.8118564390042</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>33.92560719041563</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>15.71215195376678</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.2248369848150129</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0131129154176956</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
         <v>6552</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>易華電</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="2" t="n">
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
         <v>67.11979579694513</v>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>25.15</v>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
         <v>45.31823128736141</v>
       </c>
-      <c r="I126" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>19.69693359566504</v>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J127" s="2" t="n">
         <v>0.3801624207075859</v>
       </c>
-      <c r="K126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="2" t="n">
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
         <v>0.3023020271603012</v>
       </c>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq7_2026-08-13.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-13.xlsx
@@ -1799,21 +1799,21 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6739</v>
+        <v>6781</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>565.3791324728163</v>
+        <v>531.6388249963093</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1045</v>
+        <v>1125</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>49.84933386412813</v>
+        <v>55.75784496279339</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>10.48224890951374</v>
+        <v>21.70772131656243</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.652710967577269</v>
+        <v>0.6812075675506158</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,48 +1842,48 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>13.69369593672724</v>
+        <v>27.29617318376082</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6781</v>
+        <v>6806</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>531.6388249963093</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1125</v>
+        <v>3.51</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.75784496279339</v>
+        <v>31.69502796334339</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.70772131656243</v>
+        <v>32.59319934807885</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6812075675506158</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,48 +1895,48 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>27.29617318376082</v>
+        <v>0.4112821325422744</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6806</v>
+        <v>6532</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>523.7756801768195</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>3.51</v>
+        <v>87</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>31.69502796334339</v>
+        <v>65.77557388116138</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>32.59319934807885</v>
+        <v>28.7461264035022</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>1.129839418574075</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4112821325422744</v>
+        <v>3.03091793050582</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6532</v>
+        <v>6788</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>523.7756801768195</v>
+        <v>520.9223478213482</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>87</v>
+        <v>363.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>65.77557388116138</v>
+        <v>50.67999385264918</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.7461264035022</v>
+        <v>27.76190100228168</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.129839418574075</v>
+        <v>0.572899931983292</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>3.03091793050582</v>
+        <v>6.60832176381339</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6788</v>
+        <v>6597</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>520.9223478213482</v>
+        <v>513.6677251862392</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>363.5</v>
+        <v>68</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.67999385264918</v>
+        <v>52.29117596276318</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.76190100228168</v>
+        <v>9.514012647957021</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.572899931983292</v>
+        <v>0.8444742466786808</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>6.60832176381339</v>
+        <v>0.0669386584714044</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>macd_golden_cross, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6597</v>
+        <v>6805</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>513.6677251862392</v>
+        <v>505.0779235069686</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>68</v>
+        <v>1830</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.29117596276318</v>
+        <v>63.78878098099401</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>9.514012647957021</v>
+        <v>30.85367740059933</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8444742466786808</v>
+        <v>1.27496456745889</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0669386584714044</v>
+        <v>58.5531809976468</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6805</v>
+        <v>6807</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>505.0779235069686</v>
+        <v>502.5762420098295</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1830</v>
+        <v>38</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>63.78878098099401</v>
+        <v>74.45528723082759</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>30.85367740059933</v>
+        <v>20.68179010771956</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.27496456745889</v>
+        <v>1.029481049328883</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>58.5531809976468</v>
+        <v>0.3680262636577937</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6807</v>
+        <v>6584</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>502.5762420098295</v>
+        <v>498.8866495798871</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>38</v>
+        <v>597</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>74.45528723082759</v>
+        <v>57.26355097386514</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.68179010771956</v>
+        <v>25.97599744240152</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.029481049328883</v>
+        <v>0.9192835670113714</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3680262636577937</v>
+        <v>16.55457207208008</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6584</v>
+        <v>6727</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>498.8866495798871</v>
+        <v>498.5467088339622</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.26355097386514</v>
+        <v>51.03994799281895</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>25.97599744240152</v>
+        <v>14.98299147498243</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9192835670113714</v>
+        <v>1.262028859465542</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>16.55457207208008</v>
+        <v>8.898036727459166</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6727</v>
+        <v>6672</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>498.5467088339622</v>
+        <v>486.1377628952446</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>393</v>
+        <v>264.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.03994799281895</v>
+        <v>59.94577855775164</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14.98299147498243</v>
+        <v>21.24094693341862</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.262028859465542</v>
+        <v>1.282461164337962</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>8.898036727459166</v>
+        <v>7.176983530553903</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6672</v>
+        <v>6691</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>486.1377628952446</v>
+        <v>480.2728187882935</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>264.5</v>
+        <v>728</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>59.94577855775164</v>
+        <v>55.18303777121351</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.24094693341862</v>
+        <v>13.89866219305604</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.282461164337962</v>
+        <v>0.6079809346050371</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>7.176983530553903</v>
+        <v>6.998181565526457</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6691</v>
+        <v>6829</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>480.2728187882935</v>
+        <v>479.8690620201465</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>728</v>
+        <v>222</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>55.18303777121351</v>
+        <v>59.50468669503221</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.89866219305604</v>
+        <v>16.04722161746431</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6079809346050371</v>
+        <v>1.348984324244862</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>6.998181565526457</v>
+        <v>4.736439082636447</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6829</v>
+        <v>6510</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>479.8690620201465</v>
+        <v>477.5415502922536</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>222</v>
+        <v>2820</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>59.50468669503221</v>
+        <v>51.0776328571712</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.04722161746431</v>
+        <v>20.70749092967639</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.348984324244862</v>
+        <v>0.9541737437525776</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>4.736439082636447</v>
+        <v>54.09912548711355</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6510</v>
+        <v>6589</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>477.5415502922536</v>
+        <v>472.2743222588467</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2820</v>
+        <v>50.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.0776328571712</v>
+        <v>60.11889540045873</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.70749092967639</v>
+        <v>25.77439845438841</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9541737437525776</v>
+        <v>0.9450524335911232</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>54.09912548711355</v>
+        <v>0.5729789205672249</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6589</v>
+        <v>6756</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>472.2743222588467</v>
+        <v>464.7414874519964</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>50.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>60.11889540045873</v>
+        <v>54.52769473903533</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25.77439845438841</v>
+        <v>15.14327173823001</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9450524335911232</v>
+        <v>0.9164767988572564</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.5729789205672249</v>
+        <v>0.7993497560811187</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6756</v>
+        <v>6504</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>464.7414874519964</v>
+        <v>460.414023692824</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>38.25</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.52769473903533</v>
+        <v>50.12902701378209</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15.14327173823001</v>
+        <v>28.02644348763386</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9164767988572564</v>
+        <v>0.5291468245191681</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.7993497560811187</v>
+        <v>-0.1533786258226093</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6504</v>
+        <v>6546</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>460.414023692824</v>
+        <v>452.4198637867253</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>38.25</v>
+        <v>66</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.12902701378209</v>
+        <v>57.78334092921236</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28.02644348763386</v>
+        <v>30.62753936197033</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5291468245191681</v>
+        <v>3.787708250970692</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1533786258226093</v>
+        <v>1.588575306211666</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6546</v>
+        <v>6770</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>452.4198637867253</v>
+        <v>449.7002764429392</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>66</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>57.78334092921236</v>
+        <v>61.26373929911581</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30.62753936197033</v>
+        <v>15.4769052578571</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3.787708250970692</v>
+        <v>2.270027644293921</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.588575306211666</v>
+        <v>2.13459150476115</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6770</v>
+        <v>6799</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>449.7002764429392</v>
+        <v>440.7172826187211</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>61.26373929911581</v>
+        <v>49.59145046623271</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15.4769052578571</v>
+        <v>20.05581490893999</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.270027644293921</v>
+        <v>0.2829155735352259</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>2.13459150476115</v>
+        <v>1.281423433531484</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6799</v>
+        <v>6505</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>440.7172826187211</v>
+        <v>438.1793795009783</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.59145046623271</v>
+        <v>50.07855199511643</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.05581490893999</v>
+        <v>27.7374494167803</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2829155735352259</v>
+        <v>0.2177866457636232</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.281423433531484</v>
+        <v>-1.207769330267384</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6505</v>
+        <v>6548</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>438.1793795009783</v>
+        <v>435.0521483943845</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>69.8</v>
+        <v>74.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.07855199511643</v>
+        <v>51.22499969666168</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>27.7374494167803</v>
+        <v>17.11727155639245</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2177866457636232</v>
+        <v>0.4461786441013731</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.207769330267384</v>
+        <v>1.209274448924492</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6548</v>
+        <v>6530</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>435.0521483943845</v>
+        <v>423.2836128342956</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>74.5</v>
+        <v>85.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.22499969666168</v>
+        <v>57.28944619422469</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.11727155639245</v>
+        <v>22.59302452956486</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4461786441013731</v>
+        <v>2.834847389957138</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.209274448924492</v>
+        <v>2.666565996531028</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6530</v>
+        <v>6526</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>423.2836128342956</v>
+        <v>422.329479933347</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>85.8</v>
+        <v>624</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>57.28944619422469</v>
+        <v>53.83886093575956</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.59302452956486</v>
+        <v>15.35292070175989</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.834847389957138</v>
+        <v>0.5542136234665451</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>2.666565996531028</v>
+        <v>10.59755789505117</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6526</v>
+        <v>6517</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>422.329479933347</v>
+        <v>421.5383526946082</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>624</v>
+        <v>63.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>53.83886093575956</v>
+        <v>47.08100707139351</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15.35292070175989</v>
+        <v>16.20020864520854</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5542136234665451</v>
+        <v>0.4652715652574628</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>10.59755789505117</v>
+        <v>-0.0540359291175871</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6517</v>
+        <v>6763</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>421.5383526946082</v>
+        <v>410.982191942297</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>63.7</v>
+        <v>42.85</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.08100707139351</v>
+        <v>47.82835155718937</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>16.20020864520854</v>
+        <v>25.02419889514221</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4652715652574628</v>
+        <v>0.4968266866905994</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0540359291175871</v>
+        <v>0.3283479115650549</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6763</v>
+        <v>6533</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>410.982191942297</v>
+        <v>408.2277726248292</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>42.85</v>
+        <v>249.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.82835155718937</v>
+        <v>61.70787743407196</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.02419889514221</v>
+        <v>16.565849192008</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4968266866905994</v>
+        <v>0.5453824773727142</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3283479115650549</v>
+        <v>3.322050141392706</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6533</v>
+        <v>6585</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>408.2277726248292</v>
+        <v>407.0374625518612</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>249.5</v>
+        <v>120</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>61.70787743407196</v>
+        <v>50.7236559847781</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16.565849192008</v>
+        <v>16.35072553769538</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5453824773727142</v>
+        <v>0.4345435613602557</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>3.322050141392706</v>
+        <v>0.360891012927574</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6585</v>
+        <v>6485</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>407.0374625518612</v>
+        <v>392.7865048014315</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>120</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.7236559847781</v>
+        <v>49.6143995642172</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.35072553769538</v>
+        <v>26.66269260164455</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4345435613602557</v>
+        <v>0.7241540757278374</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.360891012927574</v>
+        <v>1.873941921903262</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6485</v>
+        <v>6592</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>392.7865048014315</v>
+        <v>391.4448402195299</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.6143995642172</v>
+        <v>55.09629142754447</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>26.66269260164455</v>
+        <v>11.2072472292575</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7241540757278374</v>
+        <v>0.8069530500899972</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.873941921903262</v>
+        <v>0.2185106887053656</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6592</v>
+        <v>6689</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>391.4448402195299</v>
+        <v>389.4192521415363</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>61.7</v>
+        <v>63.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>55.09629142754447</v>
+        <v>54.5499367334045</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11.2072472292575</v>
+        <v>21.29307059250384</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8069530500899972</v>
+        <v>0.8620903063003591</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2185106887053656</v>
+        <v>0.7531867361078162</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6689</v>
+        <v>6643</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>389.4192521415363</v>
+        <v>387.8861367136258</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>63.5</v>
+        <v>447.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>54.5499367334045</v>
+        <v>52.50847002590299</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.29307059250384</v>
+        <v>18.85099116037014</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8620903063003591</v>
+        <v>0.8842863864963173</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.7531867361078162</v>
+        <v>8.588912875281599</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6643</v>
+        <v>6654</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>387.8861367136258</v>
+        <v>381.630650104766</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>447.5</v>
+        <v>181</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.50847002590299</v>
+        <v>55.53392096478769</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.85099116037014</v>
+        <v>18.34462427613047</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8842863864963173</v>
+        <v>1.155298113260916</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>8.588912875281599</v>
+        <v>1.803078900640267</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6654</v>
+        <v>6640</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>381.630650104766</v>
+        <v>377.6909510913088</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>181</v>
+        <v>995</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>55.53392096478769</v>
+        <v>53.31723503339638</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.34462427613047</v>
+        <v>19.38048023762264</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.155298113260916</v>
+        <v>1.167585064536784</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>1.803078900640267</v>
+        <v>23.69462983223441</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6640</v>
+        <v>6666</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>377.6909510913088</v>
+        <v>374.9107921081634</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>995</v>
+        <v>42.65</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.31723503339638</v>
+        <v>43.36229981576009</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.38048023762264</v>
+        <v>30.87013301758816</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.167585064536784</v>
+        <v>0.7577976623548421</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>23.69462983223441</v>
+        <v>-0.2598915014942597</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6666</v>
+        <v>6494</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>374.9107921081634</v>
+        <v>372.5334447675029</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>42.65</v>
+        <v>53.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>43.36229981576009</v>
+        <v>50.41813117354531</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>30.87013301758816</v>
+        <v>22.41955722586568</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7577976623548421</v>
+        <v>0.6059778279878705</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.2598915014942597</v>
+        <v>1.121790791764916</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6494</v>
+        <v>6693</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>372.5334447675029</v>
+        <v>371.8649085121635</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>53.9</v>
+        <v>185</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.41813117354531</v>
+        <v>51.00577670198603</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>22.41955722586568</v>
+        <v>22.46103052255724</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6059778279878705</v>
+        <v>1.497065463783021</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.121790791764916</v>
+        <v>3.192648360741991</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6693</v>
+        <v>6821</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>371.8649085121635</v>
+        <v>371.1482984064796</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.00577670198603</v>
+        <v>43.12829268495742</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.46103052255724</v>
+        <v>28.16025297565197</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.497065463783021</v>
+        <v>1.034965071400752</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>3.192648360741991</v>
+        <v>0.9324472465659132</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6821</v>
+        <v>6605</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>371.1482984064796</v>
+        <v>369.3138546373718</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>43</v>
+        <v>136.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.12829268495742</v>
+        <v>52.75947789678682</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>28.16025297565197</v>
+        <v>12.64831751216909</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.034965071400752</v>
+        <v>0.7222075861351392</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.9324472465659132</v>
+        <v>0.6233162667311183</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6605</v>
+        <v>6706</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>369.3138546373718</v>
+        <v>367.8051387928279</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>136.5</v>
+        <v>122.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.75947789678682</v>
+        <v>52.3755880663484</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.64831751216909</v>
+        <v>23.36460474397057</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7222075861351392</v>
+        <v>0.8431223528482433</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.6233162667311183</v>
+        <v>4.286729379966468</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6706</v>
+        <v>6577</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>367.8051387928279</v>
+        <v>362.4222158503363</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>122.5</v>
+        <v>79.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.3755880663484</v>
+        <v>49.40645441361617</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.36460474397057</v>
+        <v>23.08599182028461</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8431223528482433</v>
+        <v>0.1883145548949289</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>4.286729379966468</v>
+        <v>-0.2670852375813327</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6577</v>
+        <v>6830</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>362.4222158503363</v>
+        <v>360.5789029866918</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>79.5</v>
+        <v>420.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>49.40645441361617</v>
+        <v>51.47311947012582</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.08599182028461</v>
+        <v>19.25641415578155</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.1883145548949289</v>
+        <v>0.980739383128742</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.2670852375813327</v>
+        <v>13.54318826445689</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6830</v>
+        <v>6613</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>360.5789029866918</v>
+        <v>356.3800066847713</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>420.5</v>
+        <v>270.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.47311947012582</v>
+        <v>41.36222077665525</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.25641415578155</v>
+        <v>15.03463185405442</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.980739383128742</v>
+        <v>1.240759642973474</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>13.54318826445689</v>
+        <v>-2.068325791601783</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6613</v>
+        <v>6670</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>356.3800066847713</v>
+        <v>356.3071788874115</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>270.5</v>
+        <v>267</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>41.36222077665525</v>
+        <v>53.39460174768182</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.03463185405442</v>
+        <v>12.28256217748137</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.240759642973474</v>
+        <v>0.665485702499458</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-2.068325791601783</v>
+        <v>0.6848574695101624</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6670</v>
+        <v>6742</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>356.3071788874115</v>
+        <v>354.2539102248634</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>267</v>
+        <v>43.9</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.39460174768182</v>
+        <v>41.56385898418064</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>12.28256217748137</v>
+        <v>20.56808254848057</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.665485702499458</v>
+        <v>0.3713481851001997</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.6848574695101624</v>
+        <v>0.6645166947290413</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6742</v>
+        <v>6715</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>354.2539102248634</v>
+        <v>353.7694556453644</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>43.9</v>
+        <v>390.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>41.56385898418064</v>
+        <v>51.94378816463318</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20.56808254848057</v>
+        <v>10.62489755929594</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3713481851001997</v>
+        <v>1.798540505847586</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.6645166947290413</v>
+        <v>7.231007660877463</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6715</v>
+        <v>6525</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>353.7694556453644</v>
+        <v>345.720769808407</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>390.5</v>
+        <v>150.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.94378816463318</v>
+        <v>53.35845739143687</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.62489755929594</v>
+        <v>18.72929889450225</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.798540505847586</v>
+        <v>1.412132993746048</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>7.231007660877463</v>
+        <v>1.510925420472423</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6525</v>
+        <v>6531</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>345.720769808407</v>
+        <v>339.0398904390805</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>150.5</v>
+        <v>865</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,29 +4262,29 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>53.35845739143687</v>
+        <v>50.90411674180633</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.72929889450225</v>
+        <v>14.82240748094193</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.412132993746048</v>
+        <v>0.3109081902483205</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.510925420472423</v>
+        <v>18.76719476341093</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
